--- a/shadowedhistory/dark-fact-b/series_log.xlsx
+++ b/shadowedhistory/dark-fact-b/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -704,6 +704,226 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep01/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-03 15:19</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/655d1d6fec52d97e3042bf5f0da3b460_0_1791040758.mp4</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep02/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-10-03 15:21</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2ef8b01f13081edebb72296ca951f5cf_0_1791040867.mp4</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep02/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-10-03 15:24</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/1a381bf3c7db6e0dd0b8d9b566503bc5_0_1791040970.mp4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep02/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-03 15:27</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a5540dd5f93703b1724a864d3a9c1c5f_0_1791041150.mp4</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep02/shots/shot_04.mp4</t>
         </is>
       </c>
     </row>

--- a/shadowedhistory/dark-fact-b/series_log.xlsx
+++ b/shadowedhistory/dark-fact-b/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M9"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -927,6 +927,226 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-07 18:45</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e1798125d8cd83cd9397821adc35bfc7_0_1791398180.mp4</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep03/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-07 18:48</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7c0ac5ab27812127e4ac29587117dc8e_0_1791398808.mp4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep03/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-07 18:58</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d63d2ef381c683fa854b8c6bda396d22_0_1791399001.mp4</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep03/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-07 19:01</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2af7dceba8887427b86132b585aecc96_0_1791399640.mp4</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep03/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/dark-fact-b/series_log.xlsx
+++ b/shadowedhistory/dark-fact-b/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1147,6 +1147,446 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:43</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b17c732843f05f535153b21cde9cb691_0_1791567658.mp4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep04/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:45</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/84e62196c86d01544657357c323dfee7_0_1791567857.mp4</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep04/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:50</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d3df7ddfdfac8e6f108b7a766d972c32_0_1791567990.mp4</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep04/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:52</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/89c8ab7b1a027045670b8c21cff155d2_0_1791568332.mp4</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep04/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-11 16:54</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8c3fbb142c0ef4525afb9a9c6b87b470_0_1791737600.mp4</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep04/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-11 16:57</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0eeefdee19f285c496bd1e05d523409d_0_1791737786.mp4</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep04/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-11 16:59</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/daf7cc47718c61171a0492f8b1bf990a_0_1791737920.mp4</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep04/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-11 17:01</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/751a1a3fc250ce20a8ec34c13d7c7ab1_0_1791738058.mp4</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep04/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/dark-fact-b/series_log.xlsx
+++ b/shadowedhistory/dark-fact-b/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1587,6 +1587,446 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-13 18:57</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b3635b731f86df60d0e1995876f4da35_0_1791916273.mp4</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep05/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-15 15:53</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/bcf999768a890db73797d4570f6901b1_0_1792079279.mp4</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep05/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-15 16:09</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b6b7f8ae6cc7edb096a0e1d5e001f999_0_1792079825.mp4</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep05/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-15 16:15</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c7e58e1d9f72a169d8267b391e97dc23_0_1792080693.mp4</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep05/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-17 14:27</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/83e31b708c7697e2bb27181cc8caa99d_0_1792247238.mp4</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep05/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-17 14:30</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/dcd946a94fad69620af58d8271181d37_0_1792247432.mp4</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep05/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-17 14:33</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/498a24d41bd3cee93400ebcd401f3423_0_1792247555.mp4</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep05/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-17 14:36</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c92797f90d46860bd509a320c1d68218_0_1792247733.mp4</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep05/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/dark-fact-b/series_log.xlsx
+++ b/shadowedhistory/dark-fact-b/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2027,6 +2027,226 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-19 17:50</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7d39048b0891660268973f29a2ca67e2_0_1792432143.mp4</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep06/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-19 17:52</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f011a42d5baf28acbf3ce8fbf7335ee6_0_1792432294.mp4</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep06/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-19 17:55</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3ecffdfdd6220d7da4abc63cba754609_0_1792432463.mp4</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep06/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-19 17:58</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a2a8b290c460859537589b507d9cc3f8_0_1792432593.mp4</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep06/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/dark-fact-b/series_log.xlsx
+++ b/shadowedhistory/dark-fact-b/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2247,6 +2247,391 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:32</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/4e4c373c190cfe6cd6f4c4508c3db9ab_0_1793122009.mp4</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep07/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:39</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/f19628e91d0dddf37c602eae629ff225_0_1793122432.mp4</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep07/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-27 17:41</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c5a15638c75f523bbb0947b7c4828727_0_1793122855.mp4</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep07/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:46</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ce2facd65e1f072a3e4c76983009be35_0_1793295818.mp4</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep07/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-29 17:57</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8943e606ebe9b5ed27fdc5d4e8a964bf_0_1793296105.mp4</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep07/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-29 18:02</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5a4aba59390067e82140dfe2b5fca7a2_0_1793296773.mp4</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep07/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-29 18:09</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/1eb95d279303467b4c2366d783dc938a_0_1793297034.mp4</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep07/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/shadowedhistory/dark-fact-b/series_log.xlsx
+++ b/shadowedhistory/dark-fact-b/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M40"/>
+  <dimension ref="A1:M44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2632,6 +2632,226 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-31 16:29</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e12fe18cbe4d6d9a995b81a8ae2918b6_0_1793463596.mp4</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep08/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-31 16:33</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2fb8e4822eb8b593813e548274134fd5_0_1793464240.mp4</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep08/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-31 16:35</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/acdb75761e894fea4e0a1b8c3230d04d_0_1793464517.mp4</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep08/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-31 16:42</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>63.0</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0.315</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5de4f5c7ec3c975b3cf1721c61f83743_0_1793464650.mp4</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/dark-fact-b/episodes/ep08/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
